--- a/public/documents/pieces-reponse-2/R2-distributions-et-majoration.xlsx
+++ b/public/documents/pieces-reponse-2/R2-distributions-et-majoration.xlsx
@@ -58,7 +58,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -66,49 +66,26 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00DDDDDD"/>
-      </left>
-      <right style="thin">
-        <color rgb="00DDDDDD"/>
-      </right>
-      <top style="thin">
-        <color rgb="00DDDDDD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00DDDDDD"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -475,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -534,7 +511,7 @@
       <c r="D4" s="3" t="n">
         <v>139728</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="3" t="n">
         <v>471827</v>
       </c>
     </row>
@@ -553,7 +530,7 @@
       <c r="D5" s="3" t="n">
         <v>-14652</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="3" t="n">
         <v>-49927</v>
       </c>
     </row>
@@ -571,7 +548,7 @@
       <c r="D6" s="3" t="n">
         <v>125076</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="3" t="n">
         <v>421900</v>
       </c>
     </row>
@@ -590,7 +567,7 @@
       <c r="D7" s="3" t="n">
         <v>62538</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="3" t="n">
         <v>210950</v>
       </c>
     </row>
@@ -609,51 +586,51 @@
       <c r="D8" s="3" t="n">
         <v>7326</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="3" t="n">
         <v>24963</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5">
+      <c r="A9" s="4">
         <f> Base RCM par foyer</f>
         <v/>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="5" t="n">
         <v>96617</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="5" t="n">
         <v>69432</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="5" t="n">
         <v>69864</v>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="E9" s="5" t="n">
         <v>235913</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>× 1,25 → assiette IR (art. 158-7-2°)</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="5" t="n">
         <v>120771</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="5" t="n">
         <v>86790</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="5" t="n">
         <v>87330</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E10" s="5" t="n">
         <v>294891</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>CONTRÔLES (recalcul)</t>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>CONTRÔLES (recalcul vs notifié)</t>
         </is>
       </c>
     </row>
@@ -682,64 +659,64 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HT = TTC − TVA (2023) : 193 235 − 20 421</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n">
+          <t>HT 2023 = 193 235 − 20 421</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
         <v>172814</v>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="7" t="n">
         <v>172814</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Part HT = HT ÷ 2 (2023) : 172 814 ÷ 2</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n">
+          <t>Part HT 2023 = 172 814 ÷ 2</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
         <v>86407</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="7" t="n">
         <v>86407</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Base RCM = HT/2 + TVA/2 (2023) : 86 407 + 10 210</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="n">
+          <t>Base RCM 2023 = 86 407 + 10 210</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
         <v>96617</v>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="7" t="n">
         <v>96617</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Assiette IR = base × 1,25 (2023) : 96 617 × 1,25</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n">
+          <t>Assiette IR 2023 = 96 617 × 1,25</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
         <v>120771</v>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="7" t="n">
         <v>120771</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D17" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -749,29 +726,19 @@
           <t>Base RCM 3 ans par foyer</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" s="7" t="n">
         <v>235913</v>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="7" t="n">
         <v>235913</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="7" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Source : propositions de rectification personnelles du 19/10/2026 (PASTEUR &amp; BEHEM), « En matière de distributions » et art. 158-7-2° du CGI. TTC/HT repris de la reconstitution (proposition du 18/05/2026, p. 52).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A20:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -783,19 +750,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Assiette des prélèvements sociaux : le coefficient 1,25 est exclu (Cons. const. 2017-643/650 QPC)</t>
+          <t>Contrôle QPC 2017-643/650 : le coefficient 1,25 est exclu de l'assiette sociale</t>
         </is>
       </c>
     </row>
@@ -812,48 +780,114 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Base PS correcte (sans 1,25)</t>
+          <t>Assiette IR (×1,25)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>À vérifier sur la proposition</t>
+          <t>Assiette sociale retenue</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mme BEHEM — 2023</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="n">
+          <t>BEHEM 2023</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
         <v>96617</v>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C4" s="7" t="n">
+        <v>120771</v>
+      </c>
+      <c r="D4" s="7" t="n">
         <v>86407</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Base PS notifiée = 86 407 € → conforme (sans 1,25)</t>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>oui (sans 1,25)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Autres années / M. PASTEUR</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Contrôler que la CSG/CRDS/prélèvement solidarité n'est pas assis sur l'assiette × 1,25</t>
+          <t>BEHEM 2024</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>69432</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>86790</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>66088</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>oui (sans 1,25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BEHEM 2025</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>69864</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>87330</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>62538</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>oui (sans 1,25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PASTEUR 2025</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>69864</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>87330</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>69865</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>oui (sans 1,25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Conclusion : l'assiette sociale exclut le coefficient 1,25 → conforme. Pas de réduction à ce titre.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
